--- a/data/trans_camb/P2C_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 22,52</t>
+          <t>14,04; 22,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,73</t>
+          <t>1,81; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -0,3</t>
+          <t>-7,99; -0,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,21; 20,53</t>
+          <t>13,35; 20,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,44</t>
+          <t>3,6; 11,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,81</t>
+          <t>-3,85; 3,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 20,13</t>
+          <t>14,67; 20,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,7</t>
+          <t>4,19; 9,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,95</t>
+          <t>-4,14; 0,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,67; 114,65</t>
+          <t>60,11; 112,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 54,23</t>
+          <t>7,76; 49,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,77; -1,41</t>
+          <t>-34,79; -2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,23; 83,71</t>
+          <t>47,94; 84,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 46,38</t>
+          <t>12,76; 44,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 11,43</t>
+          <t>-13,77; 12,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,58; 86,57</t>
+          <t>57,76; 87,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,18; 42,23</t>
+          <t>16,43; 41,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 4,18</t>
+          <t>-16,28; 3,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,51; 18,09</t>
+          <t>11,82; 18,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,51</t>
+          <t>-3,52; 2,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,02; -19,09</t>
+          <t>-26,19; -19,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 20,86</t>
+          <t>14,34; 21,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,48</t>
+          <t>-2,83; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 4,5</t>
+          <t>-25,47; 2,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,91; 18,42</t>
+          <t>13,69; 18,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,34</t>
+          <t>-2,4; 2,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,26; -5,88</t>
+          <t>-24,38; -5,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,79; 57,6</t>
+          <t>33,92; 58,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 7,84</t>
+          <t>-10,11; 7,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,89; -59,98</t>
+          <t>-77,25; -60,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,28; 53,73</t>
+          <t>33,99; 56,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 8,89</t>
+          <t>-6,6; 9,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,08; 11,64</t>
+          <t>-62,44; 6,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,38; 52,05</t>
+          <t>35,81; 52,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 6,62</t>
+          <t>-6,24; 6,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,33; -14,93</t>
+          <t>-65,88; -16,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 16,14</t>
+          <t>4,47; 16,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 6,16</t>
+          <t>-5,18; 6,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,93; -15,26</t>
+          <t>-24,31; -14,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 19,82</t>
+          <t>7,93; 21,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 9,46</t>
+          <t>-3,11; 9,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,99; -21,28</t>
+          <t>-31,12; -21,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 17,23</t>
+          <t>7,17; 16,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,4</t>
+          <t>-2,29; 6,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,43; -19,58</t>
+          <t>-26,22; -19,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,2; 58,95</t>
+          <t>14,19; 61,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 22,07</t>
+          <t>-15,91; 22,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,21; -53,63</t>
+          <t>-73,96; -53,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,16; 58,39</t>
+          <t>19,58; 61,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 27,62</t>
+          <t>-7,34; 27,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,15; -63,32</t>
+          <t>-75,84; -63,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,77; 55,02</t>
+          <t>20,14; 53,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 20,12</t>
+          <t>-6,34; 20,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,27; -61,48</t>
+          <t>-73,18; -61,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,18</t>
+          <t>13,27; 18,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,03</t>
+          <t>-0,33; 4,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -15,09</t>
+          <t>-19,96; -14,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,42</t>
+          <t>14,71; 19,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,67</t>
+          <t>1,78; 6,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 2,19</t>
+          <t>-18,27; 1,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,8; 18,06</t>
+          <t>14,65; 18,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,82</t>
+          <t>1,56; 4,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,98; -5,94</t>
+          <t>-18,08; -6,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,02; 64,66</t>
+          <t>43,67; 64,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 14,38</t>
+          <t>-1,04; 16,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,09; -53,22</t>
+          <t>-67,85; -53,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41,1; 58,09</t>
+          <t>40,8; 57,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 19,97</t>
+          <t>5,04; 20,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 6,22</t>
+          <t>-52,3; 5,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,91; 58,1</t>
+          <t>44,79; 58,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,63</t>
+          <t>4,69; 15,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,09; -18,59</t>
+          <t>-56,33; -18,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-4,44</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-1,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 22,15</t>
+          <t>13,9; 22,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,03</t>
+          <t>2,21; 10,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -0,43</t>
+          <t>-7,83; -0,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,35; 20,84</t>
+          <t>13,24; 20,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,31</t>
+          <t>3,41; 11,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,07</t>
+          <t>-3,3; 3,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,67; 20,28</t>
+          <t>14,5; 19,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,63</t>
+          <t>3,91; 9,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,84</t>
+          <t>-4,44; 0,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-19,16%</t>
+          <t>-20,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,97%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-7,49%</t>
+          <t>-6,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,11; 112,1</t>
+          <t>59,17; 110,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 49,85</t>
+          <t>9,27; 51,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -2,33</t>
+          <t>-34,2; -1,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,94; 84,31</t>
+          <t>46,48; 83,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 44,84</t>
+          <t>12,29; 45,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 12,48</t>
+          <t>-11,59; 14,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,76; 87,83</t>
+          <t>56,1; 86,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 41,49</t>
+          <t>14,94; 41,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 3,54</t>
+          <t>-17,26; 3,56</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-22,25</t>
+          <t>-19,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,94</t>
+          <t>-23,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-19,56</t>
+          <t>-21,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,82; 18,3</t>
+          <t>11,57; 18,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,38</t>
+          <t>-3,95; 2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -19,21</t>
+          <t>-22,69; -17,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 21,6</t>
+          <t>14,24; 21,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,48</t>
+          <t>-3,06; 3,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 2,6</t>
+          <t>-26,32; -20,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,59</t>
+          <t>13,83; 18,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,15</t>
+          <t>-2,5; 2,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,38; -5,82</t>
+          <t>-23,42; -19,24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-66,67%</t>
+          <t>-59,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,02%</t>
+          <t>-57,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-53,23%</t>
+          <t>-58,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,92; 58,33</t>
+          <t>33,04; 56,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 7,46</t>
+          <t>-11,3; 7,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,25; -60,19</t>
+          <t>-65,4; -53,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,99; 56,48</t>
+          <t>33,66; 55,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 9,05</t>
+          <t>-7,24; 9,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 6,83</t>
+          <t>-62,12; -52,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 52,67</t>
+          <t>36,51; 53,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,05</t>
+          <t>-6,65; 5,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,88; -16,34</t>
+          <t>-61,85; -54,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-19,87</t>
+          <t>-19,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-26,34</t>
+          <t>-25,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-22,84</t>
+          <t>-22,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 16,68</t>
+          <t>4,09; 16,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 6,17</t>
+          <t>-4,68; 6,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,31; -14,6</t>
+          <t>-24,26; -14,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 21,06</t>
+          <t>7,06; 21,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 9,34</t>
+          <t>-2,85; 9,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,12; -21,84</t>
+          <t>-30,63; -20,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 16,56</t>
+          <t>7,22; 17,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 6,28</t>
+          <t>-1,94; 6,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,22; -19,35</t>
+          <t>-25,65; -18,79</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-65,6%</t>
+          <t>-64,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-70,36%</t>
+          <t>-68,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-67,97%</t>
+          <t>-66,51%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,19; 61,8</t>
+          <t>12,85; 60,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 22,16</t>
+          <t>-14,49; 25,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,96; -53,01</t>
+          <t>-73,43; -51,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,58; 61,93</t>
+          <t>17,08; 60,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 27,32</t>
+          <t>-6,94; 29,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,84; -63,05</t>
+          <t>-75,1; -61,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,14; 53,14</t>
+          <t>20,12; 54,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 20,13</t>
+          <t>-5,65; 19,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,18; -61,45</t>
+          <t>-72,07; -59,73</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-17,22</t>
+          <t>-15,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,84</t>
+          <t>-16,48</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,93</t>
+          <t>-16,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,27; 18,02</t>
+          <t>13,34; 18,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,54</t>
+          <t>0,01; 4,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -14,95</t>
+          <t>-17,78; -13,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,71; 19,27</t>
+          <t>14,59; 19,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,67</t>
+          <t>2,02; 6,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 1,88</t>
+          <t>-18,41; -14,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 18,05</t>
+          <t>14,81; 18,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,88</t>
+          <t>1,69; 4,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -6,01</t>
+          <t>-17,54; -14,68</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-59,05%</t>
+          <t>-53,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-37,17%</t>
+          <t>-47,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,82%</t>
+          <t>-50,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,67; 64,27</t>
+          <t>44,1; 64,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 16,29</t>
+          <t>0,01; 15,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,85; -53,09</t>
+          <t>-58,74; -48,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40,8; 57,86</t>
+          <t>40,76; 58,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 20,12</t>
+          <t>5,6; 19,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 5,68</t>
+          <t>-51,5; -43,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,79; 58,29</t>
+          <t>45,1; 59,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 15,73</t>
+          <t>5,19; 15,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-56,33; -18,87</t>
+          <t>-53,42; -47,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
